--- a/data/trans_dic/P22$concerEmp-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerEmp-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado por su empresa</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado por su empresa (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,55</t>
+          <t>0,3; 2,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 3,11</t>
+          <t>0,06; 2,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,78</t>
+          <t>0,18; 1,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,43</t>
+          <t>0,15; 1,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,79</t>
+          <t>0,18; 2,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,8</t>
+          <t>0,14; 1,65</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,56</t>
+          <t>1,01; 3,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,78</t>
+          <t>0,25; 2,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,6</t>
+          <t>0,43; 2,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,94</t>
+          <t>0,53; 1,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,56</t>
+          <t>0,2; 1,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,58</t>
+          <t>0,31; 1,6</t>
         </is>
       </c>
     </row>
@@ -997,47 +997,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,74</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,37</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,45</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,02</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,86</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,82</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 0,57</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,11</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,52</t>
+          <t>0,26; 2,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,6</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,76</t>
+          <t>0,29; 1,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,69</t>
+          <t>0,31; 2,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,02</t>
+          <t>0,54; 3,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,78</t>
+          <t>1,04; 5,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,22</t>
+          <t>0,65; 5,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,07</t>
+          <t>0,57; 3,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,27</t>
+          <t>0,11; 1,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,35</t>
+          <t>0,67; 2,28</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,92</t>
+          <t>0,4; 1,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,73</t>
+          <t>0,7; 2,65</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,53</t>
+          <t>0,5; 2,55</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 9,06</t>
+          <t>2,38; 9,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,46</t>
+          <t>0,45; 4,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,66</t>
+          <t>1,84; 5,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,58</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
     </row>
@@ -1417,52 +1417,52 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,63</t>
+          <t>0,17; 1,53</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,59</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,98</t>
+          <t>0,31; 1,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,39</t>
+          <t>0,15; 1,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,43</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,02</t>
+          <t>2,44; 5,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,18</t>
+          <t>0,15; 1,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,56</t>
+          <t>0,6; 2,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,18</t>
+          <t>0,29; 1,19</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,12</t>
+          <t>0,15; 1,03</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,54</t>
+          <t>1,45; 3,52</t>
         </is>
       </c>
     </row>
@@ -1697,27 +1697,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,78</t>
+          <t>5,03; 8,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,11</t>
+          <t>0,38; 2,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,52</t>
+          <t>0,17; 1,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,82</t>
+          <t>0,46; 1,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1727,32 +1727,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,45</t>
+          <t>0,28; 1,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,86; 4,82</t>
+          <t>2,81; 4,75</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,21</t>
+          <t>0,27; 1,25</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,63</t>
+          <t>0,07; 0,62</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,17</t>
+          <t>0,31; 1,18</t>
         </is>
       </c>
     </row>
@@ -1837,52 +1837,52 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,8</t>
+          <t>1,77; 2,79</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,57</t>
+          <t>0,84; 1,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,92</t>
+          <t>0,31; 0,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,93</t>
+          <t>0,93; 1,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,86</t>
+          <t>0,34; 0,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,62</t>
+          <t>0,22; 0,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,59</t>
+          <t>0,2; 0,6</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,91</t>
+          <t>0,43; 0,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,68</t>
+          <t>1,11; 1,7</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,02</t>
+          <t>0,56; 0,99</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,29</t>
+          <t>0,78; 1,3</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado por su empresa</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado por su empresa (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6236</t>
+          <t>0; 6308</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>882; 7527</t>
+          <t>875; 7457</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>966; 9764</t>
+          <t>980; 9741</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>172; 9683</t>
+          <t>174; 9011</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6126</t>
+          <t>0; 7168</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2145</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5868</t>
+          <t>0; 5208</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2696</t>
+          <t>0; 2936</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1008; 9461</t>
+          <t>944; 9363</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>886; 8297</t>
+          <t>888; 8383</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1001; 10424</t>
+          <t>1065; 12053</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>530; 10829</t>
+          <t>823; 9903</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4228; 17555</t>
+          <t>5004; 19160</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1871; 14051</t>
+          <t>1265; 14357</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2027</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2308; 13501</t>
+          <t>2204; 13393</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4934</t>
+          <t>0; 4570</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6374</t>
+          <t>0; 5183</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4986</t>
+          <t>0; 4281</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5080; 19298</t>
+          <t>5266; 19202</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2255; 16017</t>
+          <t>2057; 15806</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 2052</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3449; 16338</t>
+          <t>3255; 16500</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1968</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6546</t>
+          <t>0; 5634</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 9054</t>
+          <t>0; 7518</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5754</t>
+          <t>0; 4593</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1916</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7189</t>
+          <t>0; 6881</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>888; 8474</t>
+          <t>879; 7597</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5599</t>
+          <t>0; 6958</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1945</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>944; 8758</t>
+          <t>943; 8789</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1751; 11481</t>
+          <t>1865; 12531</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 7409</t>
+          <t>0; 7555</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1102; 9588</t>
+          <t>1091; 9993</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1971; 11301</t>
+          <t>2015; 11283</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3946; 17668</t>
+          <t>3849; 19131</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2648; 16309</t>
+          <t>2041; 15857</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1941; 11367</t>
+          <t>2107; 11860</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6594</t>
+          <t>0; 7222</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6235</t>
+          <t>0; 6526</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>710; 6021</t>
+          <t>533; 6112</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4368; 17087</t>
+          <t>4869; 16593</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3104; 14660</t>
+          <t>3088; 13838</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5581; 20694</t>
+          <t>5279; 20062</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3973; 19954</t>
+          <t>3910; 20092</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6526</t>
+          <t>0; 6759</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5098; 19259</t>
+          <t>5067; 19566</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1903</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3646</t>
+          <t>0; 3782</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2002</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1011; 9785</t>
+          <t>990; 9658</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4712</t>
+          <t>0; 5380</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 813</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6554</t>
+          <t>0; 7069</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7898; 24484</t>
+          <t>7939; 23576</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 6782</t>
+          <t>0; 3583</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3273</t>
+          <t>0; 3283</t>
         </is>
       </c>
     </row>
@@ -3249,52 +3249,52 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5648</t>
+          <t>0; 5807</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6299</t>
+          <t>0; 7046</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1942</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 1391</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1970</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5077</t>
+          <t>0; 5734</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5717</t>
+          <t>0; 4160</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3115</t>
+          <t>0; 3031</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6328</t>
+          <t>0; 7082</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>945; 9026</t>
+          <t>952; 8483</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3246</t>
+          <t>0; 3130</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2686; 12162</t>
+          <t>1898; 11465</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1000; 9238</t>
+          <t>1016; 10716</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 9317</t>
+          <t>0; 10144</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15214; 37566</t>
+          <t>15203; 36639</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 6663</t>
+          <t>0; 7253</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4930</t>
+          <t>0; 4836</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1004; 8088</t>
+          <t>998; 8141</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>4798; 21713</t>
+          <t>5055; 20784</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3715; 14801</t>
+          <t>3632; 14910</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1917; 11137</t>
+          <t>1951; 11070</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2044; 14977</t>
+          <t>2052; 13750</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>20106; 52150</t>
+          <t>21369; 51845</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>36680; 65075</t>
+          <t>37279; 63970</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2977; 16452</t>
+          <t>2980; 17123</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 7597</t>
+          <t>0; 7000</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1639; 14093</t>
+          <t>1537; 13494</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3582; 14286</t>
+          <t>3585; 15037</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 7946</t>
+          <t>0; 7916</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 7780</t>
+          <t>0; 7930</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2077; 10373</t>
+          <t>1992; 9592</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>43596; 73465</t>
+          <t>42829; 72469</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4098; 19405</t>
+          <t>4363; 20014</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1089; 10110</t>
+          <t>1086; 9972</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5291; 19248</t>
+          <t>5152; 19401</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>58910; 91539</t>
+          <t>57796; 91154</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>27146; 53641</t>
+          <t>28703; 54769</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11358; 31139</t>
+          <t>10391; 31425</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33658; 66724</t>
+          <t>32078; 65780</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11173; 28937</t>
+          <t>11325; 29491</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7093; 22154</t>
+          <t>7912; 22079</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6866; 21055</t>
+          <t>7040; 21098</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>15751; 33438</t>
+          <t>15663; 33003</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>74200; 112004</t>
+          <t>73991; 113186</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>38600; 70893</t>
+          <t>38861; 69011</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22121; 45723</t>
+          <t>21825; 45532</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>56288; 91591</t>
+          <t>55461; 92328</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$concerEmp-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerEmp-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,17 +727,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,32</t>
+          <t>0,33; 3,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 2,89</t>
+          <t>0,26; 2,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,76</t>
+          <t>0,18; 1,64</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,44</t>
+          <t>0,15; 1,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,07</t>
+          <t>0,18; 1,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,65</t>
+          <t>0,17; 1,48</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,89</t>
+          <t>0,86; 3,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,85</t>
+          <t>0,39; 2,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,58</t>
+          <t>0,41; 2,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,91</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,93</t>
+          <t>0,53; 1,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,54</t>
+          <t>0,22; 1,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,6</t>
+          <t>0,26; 1,37</t>
         </is>
       </c>
     </row>
@@ -944,27 +944,27 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,26</t>
+          <t>0,26; 2,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,32</t>
+          <t>0,15; 1,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,92</t>
+          <t>0,27; 1,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,23</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,8</t>
+          <t>0,26; 2,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,02</t>
+          <t>0,52; 3,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,17</t>
+          <t>1,06; 5,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,07</t>
+          <t>0,59; 4,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,2</t>
+          <t>0,57; 3,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,28</t>
+          <t>0,14; 1,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,28</t>
+          <t>0,58; 2,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,81</t>
+          <t>0,4; 1,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,65</t>
+          <t>0,64; 2,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,55</t>
+          <t>0,59; 2,76</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 9,2</t>
+          <t>2,43; 9,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,4</t>
+          <t>0,46; 4,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,46</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,45</t>
+          <t>1,84; 5,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 1,24</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1442,27 +1442,27 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,53</t>
+          <t>0,17; 1,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,87</t>
+          <t>0,44; 1,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,62</t>
+          <t>0,15; 1,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1572,47 +1572,47 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,87</t>
+          <t>2,35; 5,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,19</t>
+          <t>0,15; 1,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,45</t>
+          <t>1,1; 2,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,19</t>
+          <t>0,3; 1,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,82</t>
+          <t>0,14; 0,88</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,03</t>
+          <t>0,15; 0,99</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,52</t>
+          <t>1,91; 3,74</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,63</t>
+          <t>4,97; 8,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,2</t>
+          <t>0,38; 2,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,9</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,45</t>
+          <t>0,29; 1,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,92</t>
+          <t>0,42; 1,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,34</t>
+          <t>0,27; 1,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,75</t>
+          <t>2,82; 4,88</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,25</t>
+          <t>0,26; 1,2</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,62</t>
+          <t>0,07; 0,73</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,18</t>
+          <t>0,39; 1,32</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,79</t>
+          <t>1,76; 2,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,6</t>
+          <t>0,8; 1,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,93</t>
+          <t>0,32; 0,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,9</t>
+          <t>1,08; 2,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,87</t>
+          <t>0,32; 0,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,62</t>
+          <t>0,19; 0,59</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,6</t>
+          <t>0,19; 0,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,9</t>
+          <t>0,47; 0,96</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,7</t>
+          <t>1,1; 1,7</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,99</t>
+          <t>0,55; 0,99</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,66</t>
+          <t>0,32; 0,7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,3</t>
+          <t>0,81; 1,32</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>522</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3675</t>
         </is>
       </c>
     </row>
@@ -2209,27 +2209,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 6308</t>
+          <t>0; 6397</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>875; 7457</t>
+          <t>880; 7443</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>980; 9741</t>
+          <t>981; 10156</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>174; 9011</t>
+          <t>837; 8354</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7168</t>
+          <t>0; 7256</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2239,32 +2239,32 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5208</t>
+          <t>0; 6045</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2936</t>
+          <t>0; 2916</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>944; 9363</t>
+          <t>942; 8758</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>888; 8383</t>
+          <t>885; 8038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1065; 12053</t>
+          <t>1055; 11245</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>823; 9903</t>
+          <t>1064; 9412</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7575</t>
+          <t>7438</t>
         </is>
       </c>
     </row>
@@ -2417,12 +2417,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5004; 19160</t>
+          <t>4263; 19150</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1265; 14357</t>
+          <t>1990; 14064</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2432,17 +2432,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2204; 13393</t>
+          <t>2159; 14130</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4570</t>
+          <t>0; 5123</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5183</t>
+          <t>0; 5262</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -2452,17 +2452,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4281</t>
+          <t>0; 4209</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5266; 19202</t>
+          <t>5284; 19697</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2057; 15806</t>
+          <t>2212; 15439</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3255; 16500</t>
+          <t>2779; 14726</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2391</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5634</t>
+          <t>0; 6558</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 7518</t>
+          <t>0; 8349</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4593</t>
+          <t>0; 6257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 6881</t>
+          <t>0; 6914</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>879; 7597</t>
+          <t>875; 8077</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 6958</t>
+          <t>0; 7130</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>943; 8789</t>
+          <t>975; 8788</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1865; 12531</t>
+          <t>1785; 11886</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 7555</t>
+          <t>0; 8266</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9328</t>
+          <t>10226</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1091; 9993</t>
+          <t>939; 9661</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2015; 11283</t>
+          <t>1940; 12377</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3849; 19131</t>
+          <t>3922; 18682</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2041; 15857</t>
+          <t>2192; 18126</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2107; 11860</t>
+          <t>2113; 11624</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 7222</t>
+          <t>0; 7297</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6526</t>
+          <t>0; 6185</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>533; 6112</t>
+          <t>573; 7099</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4869; 16593</t>
+          <t>4232; 16405</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3088; 13838</t>
+          <t>3050; 14772</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5279; 20062</t>
+          <t>4811; 20406</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3910; 20092</t>
+          <t>4685; 21968</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>704</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>704</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6759</t>
+          <t>0; 5762</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5067; 19566</t>
+          <t>5157; 19394</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3782</t>
+          <t>0; 3530</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3066,12 +3066,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>990; 9658</t>
+          <t>1013; 9723</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5380</t>
+          <t>0; 4447</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3081,22 +3081,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 7069</t>
+          <t>0; 6484</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7939; 23576</t>
+          <t>7972; 23082</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 3583</t>
+          <t>0; 5344</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3283</t>
+          <t>0; 3534</t>
         </is>
       </c>
     </row>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>606</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>606</t>
         </is>
       </c>
     </row>
@@ -3249,12 +3249,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5807</t>
+          <t>0; 6757</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 7046</t>
+          <t>0; 7379</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3274,37 +3274,37 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5734</t>
+          <t>0; 4815</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4160</t>
+          <t>0; 5793</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3031</t>
+          <t>0; 3640</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 7082</t>
+          <t>0; 6300</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>952; 8483</t>
+          <t>950; 8136</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5117</t>
+          <t>0; 5075</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3130</t>
+          <t>0; 3727</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24373</t>
+          <t>26695</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>12446</t>
+          <t>13432</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>36819</t>
+          <t>40127</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1898; 11465</t>
+          <t>2708; 12183</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1016; 10716</t>
+          <t>1018; 9108</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 10144</t>
+          <t>0; 10124</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15203; 36639</t>
+          <t>16914; 40105</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 7253</t>
+          <t>0; 6401</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4836</t>
+          <t>0; 4907</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>998; 8141</t>
+          <t>997; 8763</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5055; 20784</t>
+          <t>8443; 22497</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3632; 14910</t>
+          <t>3764; 14824</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1951; 11070</t>
+          <t>1960; 11917</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2052; 13750</t>
+          <t>2016; 13315</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21369; 51845</t>
+          <t>28522; 55757</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>4786</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>12254</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>37279; 63970</t>
+          <t>36870; 63652</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2980; 17123</t>
+          <t>2960; 16822</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 7000</t>
+          <t>0; 8130</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1537; 13494</t>
+          <t>2308; 13810</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3585; 15037</t>
+          <t>3322; 14691</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 7916</t>
+          <t>0; 7636</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 7930</t>
+          <t>0; 8144</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1992; 9592</t>
+          <t>2277; 10646</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42829; 72469</t>
+          <t>42944; 74360</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4363; 20014</t>
+          <t>4158; 19299</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1086; 9972</t>
+          <t>1085; 11707</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5152; 19401</t>
+          <t>6299; 21439</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48766</t>
+          <t>52667</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>71966</t>
+          <t>77422</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>57796; 91154</t>
+          <t>57515; 93141</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>28703; 54769</t>
+          <t>27511; 55618</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10391; 31425</t>
+          <t>10884; 32188</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32078; 65780</t>
+          <t>38292; 72093</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>11325; 29491</t>
+          <t>10797; 28701</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7912; 22079</t>
+          <t>6884; 21084</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7040; 21098</t>
+          <t>6799; 20757</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>15663; 33003</t>
+          <t>17557; 35815</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>73991; 113186</t>
+          <t>73090; 113063</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>38861; 69011</t>
+          <t>38721; 69164</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21825; 45532</t>
+          <t>22216; 48325</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>55461; 92328</t>
+          <t>58899; 95990</t>
         </is>
       </c>
     </row>
